--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-acidfast.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
